--- a/labs/lab-02-word-to-powerpoint-and-outlook/data/Northstar_Work_Orders.xlsx
+++ b/labs/lab-02-word-to-powerpoint-and-outlook/data/Northstar_Work_Orders.xlsx
@@ -13,15 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt_Log" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence_Log" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'About_This_Data'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Work_Orders'!$A$1:$M$121</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Technicians'!$A$1:$D$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Control'!$A$1:$B$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Prompt_Log'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Checks'!$A$1:$C$2</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -561,7 +555,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1331,7 +1324,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="F14" s="2"/>
       <c r="G14" s="4" t="n">
         <v>46278</v>
       </c>
@@ -1971,7 +1964,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="F26" s="2"/>
       <c r="G26" s="4" t="n">
         <v>46266</v>
       </c>
@@ -3259,7 +3252,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr"/>
+      <c r="F50" s="2"/>
       <c r="G50" s="4" t="n">
         <v>46242</v>
       </c>
@@ -4547,7 +4540,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr"/>
+      <c r="F74" s="2"/>
       <c r="G74" s="4" t="n">
         <v>46218</v>
       </c>
@@ -5187,7 +5180,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr"/>
+      <c r="F86" s="2"/>
       <c r="G86" s="4" t="n">
         <v>46286</v>
       </c>
@@ -6475,7 +6468,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr"/>
+      <c r="F110" s="2"/>
       <c r="G110" s="4" t="n">
         <v>46262</v>
       </c>
@@ -7090,7 +7083,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7296,7 +7288,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7478,7 +7469,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7600,7 +7590,11 @@
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>OUTLOOK COPILOT:
-Draft a concise reply to the synthetic thread quoted below, using the verified Northstar brief and these checked metrics. State the 30 September 2026 scope, backlog/overdue findings, proposed next actions and the decision requested. Explain that assignments are unapproved proposals. Do not claim the attachments have been sent. Keep as a draft.</t>
+Draft a concise reply to the synthetic thread quoted below, using the verified Northstar brief and these checked metrics. State the 30 September 2026 scope, backlog/overdue findings, proposed next actions and the decision requested. Explain that assignments are unapproved proposals. Do not claim the attachments have been sent. Keep as a draft.
+THREAD (synthetic, do not send):
+2026-09-29 09:00 Operations manager: Please prepare the 30 September portfolio snapshot; show open work by site, category and current assignment.
+2026-09-29 10:15 Supervisor: Check overdue jobs before proposing reassignment. Available hours are planning inputs, not approval.
+2026-09-30 08:30 Analyst: The source export is in the workbook. No new assignment has been approved. Please produce a Word brief and a short PowerPoint update, then prepare a draft reply.</t>
         </is>
       </c>
     </row>
@@ -7623,7 +7617,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7667,12 +7660,82 @@
       </c>
       <c r="B2" s="2">
         <f>ROWS(tblWorkOrders[Work_Order_ID])</f>
-        <v/>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      </c>
+      <c r="C2" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Claim_or_Test</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Observed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source_and_Scope</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>As_At</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Verified_By</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/labs/lab-02-word-to-powerpoint-and-outlook/data/Northstar_Work_Orders.xlsx
+++ b/labs/lab-02-word-to-powerpoint-and-outlook/data/Northstar_Work_Orders.xlsx
@@ -545,12 +545,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Rejoin</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>This input is a deterministic checkpoint, not proof of your Copilot output.</t>
+          <t>Work on a copy saved to your OneDrive folder; keep this supplied workbook unchanged.</t>
         </is>
       </c>
     </row>

--- a/labs/lab-02-word-to-powerpoint-and-outlook/data/Northstar_Work_Orders.xlsx
+++ b/labs/lab-02-word-to-powerpoint-and-outlook/data/Northstar_Work_Orders.xlsx
@@ -8,12 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About_This_Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Work_Orders" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Technicians" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt_Log" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence_Log" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Export" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Work_Orders" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Technicians" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt_Log" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence_Log" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,8 +23,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="&quot;S$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -75,6 +77,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -477,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -550,7 +558,19 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Work on a copy saved to your OneDrive folder; keep this supplied workbook unchanged.</t>
+          <t>Synthetic training data. Work on this file in your lab folder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Lab 1 result</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Completed Lab 1 workbook: 2 exact duplicate records removed (WO-2026-0005, WO-2026-0020) and 2 category labels standardised (WO-2026-0004, WO-2026-0013). Supplied so this lab can start straight away.</t>
         </is>
       </c>
     </row>
@@ -560,6 +580,6640 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M123"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Work_Order_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Job_Category</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Assigned_To</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Opened_Date</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Due_Date</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Closed_Date</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Estimated_Hours</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Actual_Hours</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Cost_SGD</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Aisha Tan</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>46290</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair scheduled or reactive task 001</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Ben Lim</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>46289</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair scheduled or reactive task 002</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Chloe Goh</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>46288</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair scheduled or reactive task 003</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Leak repair </t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Lee</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>196.5</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair scheduled or reactive task 004</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Elena Ong</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>46286</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 005</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Farid Rahman</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>46285</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>267.5</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 006</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Grace Ng</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>46284</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 007</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Hari Kumar</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>46283</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 008</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Aisha Tan</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>46282</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>374</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement scheduled or reactive task 009</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Ben Lim</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>46281</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>409.5</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement scheduled or reactive task 010</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Chloe Goh</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>46280</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>445</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement scheduled or reactive task 011</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Lee</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>46279</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>480.5</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement scheduled or reactive task 012</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pump service </t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="4" t="n">
+        <v>46278</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>516</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service scheduled or reactive task 013</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Farid Rahman</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service scheduled or reactive task 014</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Grace Ng</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>46276</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service scheduled or reactive task 015</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0016</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Hari Kumar</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>46275</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>46288</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service scheduled or reactive task 016</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0017</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Aisha Tan</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>46288</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>196.5</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 017</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0018</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Ben Lim</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>46273</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 018</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0019</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Chloe Goh</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>46272</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>267.5</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 019</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0020</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Lee</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>46271</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 020</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0021</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Elena Ong</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>46270</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>46279</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair scheduled or reactive task 021</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0022</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Farid Rahman</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>46269</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>46279</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>374</v>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair scheduled or reactive task 022</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0023</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Grace Ng</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>46268</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>409.5</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair scheduled or reactive task 023</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0024</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Hari Kumar</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>445</v>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair scheduled or reactive task 024</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0025</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>480.5</v>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 025</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Ben Lim</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>46275</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>516</v>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0027</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Chloe Goh</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>46264</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>46275</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 027</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0028</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Lee</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>46263</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 028</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0029</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Elena Ong</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>46262</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement scheduled or reactive task 029</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0030</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Farid Rahman</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>46261</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>196.5</v>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement scheduled or reactive task 030</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Grace Ng</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement scheduled or reactive task 031</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0032</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Hari Kumar</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>46259</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>267.5</v>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement scheduled or reactive task 032</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0033</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Aisha Tan</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>46258</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service scheduled or reactive task 033</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0034</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Ben Lim</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>46257</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service scheduled or reactive task 034</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Chloe Goh</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>46256</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>374</v>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service scheduled or reactive task 035</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Lee</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>46255</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>409.5</v>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service scheduled or reactive task 036</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0037</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Elena Ong</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>46254</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>445</v>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 037</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0038</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Farid Rahman</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>46253</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>480.5</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 038</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0039</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Grace Ng</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>46252</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>516</v>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 039</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Hari Kumar</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>46251</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 040</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0041</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Aisha Tan</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>46250</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>46257</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>46258</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair scheduled or reactive task 041</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0042</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Ben Lim</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>46249</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>46257</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>46258</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair scheduled or reactive task 042</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0043</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Chloe Goh</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>46248</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>46257</v>
+      </c>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>196.5</v>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair scheduled or reactive task 043</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0044</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Lee</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>46257</v>
+      </c>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair scheduled or reactive task 044</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0045</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Elena Ong</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>46257</v>
+      </c>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>267.5</v>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 045</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0046</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Farid Rahman</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>46245</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>46257</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>46259</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 046</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0047</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Grace Ng</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>46257</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>46259</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 047</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0048</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Hari Kumar</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>46243</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>46257</v>
+      </c>
+      <c r="I49" s="2" t="n"/>
+      <c r="J49" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>374</v>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 048</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0049</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F50" s="2"/>
+      <c r="G50" s="4" t="n">
+        <v>46242</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>46257</v>
+      </c>
+      <c r="I50" s="2" t="n"/>
+      <c r="J50" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>409.5</v>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement scheduled or reactive task 049</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0050</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Ben Lim</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>46257</v>
+      </c>
+      <c r="I51" s="2" t="n"/>
+      <c r="J51" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>445</v>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement scheduled or reactive task 050</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0051</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Chloe Goh</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>46247</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>46245</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>480.5</v>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement scheduled or reactive task 051</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0052</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Lee</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>46247</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>46245</v>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>516</v>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement scheduled or reactive task 052</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0053</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Elena Ong</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>46247</v>
+      </c>
+      <c r="I54" s="2" t="n"/>
+      <c r="J54" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service scheduled or reactive task 053</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0054</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Farid Rahman</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>46247</v>
+      </c>
+      <c r="I55" s="2" t="n"/>
+      <c r="J55" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service scheduled or reactive task 054</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0055</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Grace Ng</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>46236</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>46247</v>
+      </c>
+      <c r="I56" s="2" t="n"/>
+      <c r="J56" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service scheduled or reactive task 055</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0056</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Hari Kumar</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>46247</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>46246</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>196.5</v>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service scheduled or reactive task 056</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0057</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Aisha Tan</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>46247</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>46246</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 057</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0058</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Ben Lim</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>46233</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>46247</v>
+      </c>
+      <c r="I59" s="2" t="n"/>
+      <c r="J59" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>267.5</v>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 058</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0059</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Chloe Goh</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>46232</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>46247</v>
+      </c>
+      <c r="I60" s="2" t="n"/>
+      <c r="J60" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 059</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0060</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Lee</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>46231</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>46247</v>
+      </c>
+      <c r="I61" s="2" t="n"/>
+      <c r="J61" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 060</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0061</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Elena Ong</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>374</v>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair scheduled or reactive task 061</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0062</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Farid Rahman</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>46229</v>
+      </c>
+      <c r="H63" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>409.5</v>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair scheduled or reactive task 062</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0063</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Grace Ng</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>46228</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="I64" s="2" t="n"/>
+      <c r="J64" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>445</v>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair scheduled or reactive task 063</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0064</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Hari Kumar</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>46227</v>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="I65" s="2" t="n"/>
+      <c r="J65" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>480.5</v>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair scheduled or reactive task 064</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0065</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Aisha Tan</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>46226</v>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="I66" s="2" t="n"/>
+      <c r="J66" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>516</v>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 065</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0066</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Ben Lim</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>46225</v>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="I67" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 066</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0067</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Chloe Goh</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>46224</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 067</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0068</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Lee</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>46223</v>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="I69" s="2" t="n"/>
+      <c r="J69" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 068</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0069</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Elena Ong</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>46222</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="I70" s="2" t="n"/>
+      <c r="J70" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>196.5</v>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement scheduled or reactive task 069</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0070</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Farid Rahman</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>46221</v>
+      </c>
+      <c r="H71" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="I71" s="2" t="n"/>
+      <c r="J71" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement scheduled or reactive task 070</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0071</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Grace Ng</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>46220</v>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>46227</v>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>46229</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>267.5</v>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement scheduled or reactive task 071</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0072</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Hari Kumar</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>46219</v>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>46227</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>46229</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement scheduled or reactive task 072</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0073</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F74" s="2"/>
+      <c r="G74" s="4" t="n">
+        <v>46218</v>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>46227</v>
+      </c>
+      <c r="I74" s="2" t="n"/>
+      <c r="J74" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service scheduled or reactive task 073</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0074</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Ben Lim</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>46217</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>46227</v>
+      </c>
+      <c r="I75" s="2" t="n"/>
+      <c r="J75" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>374</v>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service scheduled or reactive task 074</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0075</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Chloe Goh</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>46216</v>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>46227</v>
+      </c>
+      <c r="I76" s="2" t="n"/>
+      <c r="J76" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>409.5</v>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service scheduled or reactive task 075</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0076</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Lee</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>46215</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>46227</v>
+      </c>
+      <c r="I77" s="4" t="n">
+        <v>46225</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>445</v>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service scheduled or reactive task 076</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0077</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Elena Ong</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>46214</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>46227</v>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>46225</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>480.5</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 077</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0078</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Farid Rahman</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>46213</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>46227</v>
+      </c>
+      <c r="I79" s="2" t="n"/>
+      <c r="J79" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>516</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 078</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0079</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Grace Ng</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>46212</v>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>46227</v>
+      </c>
+      <c r="I80" s="2" t="n"/>
+      <c r="J80" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 079</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0080</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Hari Kumar</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>46211</v>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>46227</v>
+      </c>
+      <c r="I81" s="2" t="n"/>
+      <c r="J81" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 080</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0081</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Aisha Tan</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>46290</v>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I82" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair scheduled or reactive task 081</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0082</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Ben Lim</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>46289</v>
+      </c>
+      <c r="H83" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I83" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>196.5</v>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair scheduled or reactive task 082</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0083</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Chloe Goh</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>46288</v>
+      </c>
+      <c r="H84" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I84" s="2" t="n"/>
+      <c r="J84" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair scheduled or reactive task 083</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0084</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Lee</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="H85" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I85" s="2" t="n"/>
+      <c r="J85" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>267.5</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair scheduled or reactive task 084</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0085</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F86" s="2"/>
+      <c r="G86" s="4" t="n">
+        <v>46286</v>
+      </c>
+      <c r="H86" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I86" s="2" t="n"/>
+      <c r="J86" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 085</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0086</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Farid Rahman</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>46285</v>
+      </c>
+      <c r="H87" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I87" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 086</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0087</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Grace Ng</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>46284</v>
+      </c>
+      <c r="H88" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I88" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>374</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 087</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0088</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Hari Kumar</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>46283</v>
+      </c>
+      <c r="H89" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I89" s="2" t="n"/>
+      <c r="J89" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>409.5</v>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 088</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0089</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Aisha Tan</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>46282</v>
+      </c>
+      <c r="H90" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I90" s="2" t="n"/>
+      <c r="J90" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>445</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement scheduled or reactive task 089</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0090</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Ben Lim</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="n">
+        <v>46281</v>
+      </c>
+      <c r="H91" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I91" s="2" t="n"/>
+      <c r="J91" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>480.5</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement scheduled or reactive task 090</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0091</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Chloe Goh</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>46280</v>
+      </c>
+      <c r="H92" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="I92" s="4" t="n">
+        <v>46288</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>516</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement scheduled or reactive task 091</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0092</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Lee</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>46279</v>
+      </c>
+      <c r="H93" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="I93" s="4" t="n">
+        <v>46288</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement scheduled or reactive task 092</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0093</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Elena Ong</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>46278</v>
+      </c>
+      <c r="H94" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="I94" s="2" t="n"/>
+      <c r="J94" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service scheduled or reactive task 093</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0094</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Farid Rahman</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="H95" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="I95" s="2" t="n"/>
+      <c r="J95" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service scheduled or reactive task 094</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0095</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Grace Ng</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>46276</v>
+      </c>
+      <c r="H96" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="I96" s="2" t="n"/>
+      <c r="J96" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>196.5</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service scheduled or reactive task 095</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0096</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Hari Kumar</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>46275</v>
+      </c>
+      <c r="H97" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="I97" s="4" t="n">
+        <v>46289</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service scheduled or reactive task 096</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0097</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Aisha Tan</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="I98" s="4" t="n">
+        <v>46289</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>267.5</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 097</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0098</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Ben Lim</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>46273</v>
+      </c>
+      <c r="H99" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="I99" s="2" t="n"/>
+      <c r="J99" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 098</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0099</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Chloe Goh</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>46272</v>
+      </c>
+      <c r="H100" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="I100" s="2" t="n"/>
+      <c r="J100" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 099</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0100</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Lee</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>46271</v>
+      </c>
+      <c r="H101" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="I101" s="2" t="n"/>
+      <c r="J101" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>374</v>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0101</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Elena Ong</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>46270</v>
+      </c>
+      <c r="H102" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="I102" s="4" t="n">
+        <v>46275</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>409.5</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair scheduled or reactive task 101</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0102</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Farid Rahman</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>46269</v>
+      </c>
+      <c r="H103" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="I103" s="4" t="n">
+        <v>46275</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>445</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair scheduled or reactive task 102</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0103</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Grace Ng</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>46268</v>
+      </c>
+      <c r="H104" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="I104" s="2" t="n"/>
+      <c r="J104" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>480.5</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair scheduled or reactive task 103</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0104</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Hari Kumar</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="H105" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="I105" s="2" t="n"/>
+      <c r="J105" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>516</v>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>Leak Repair scheduled or reactive task 104</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0105</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Aisha Tan</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="H106" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="I106" s="2" t="n"/>
+      <c r="J106" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 105</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0106</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Ben Lim</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H107" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="I107" s="4" t="n">
+        <v>46276</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 106</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0107</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Chloe Goh</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="n">
+        <v>46264</v>
+      </c>
+      <c r="H108" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="I108" s="4" t="n">
+        <v>46276</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 107</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0108</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Woodlands Hub</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Lee</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="n">
+        <v>46263</v>
+      </c>
+      <c r="H109" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="I109" s="2" t="n"/>
+      <c r="J109" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>196.5</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 108</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0109</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F110" s="2"/>
+      <c r="G110" s="4" t="n">
+        <v>46262</v>
+      </c>
+      <c r="H110" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="I110" s="2" t="n"/>
+      <c r="J110" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement scheduled or reactive task 109</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0110</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Farid Rahman</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="n">
+        <v>46261</v>
+      </c>
+      <c r="H111" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="I111" s="2" t="n"/>
+      <c r="J111" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>267.5</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement scheduled or reactive task 110</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0111</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Grace Ng</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H112" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="I112" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement scheduled or reactive task 111</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0112</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Hari Kumar</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="n">
+        <v>46259</v>
+      </c>
+      <c r="H113" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="I113" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>Pipe Replacement scheduled or reactive task 112</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0113</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Aisha Tan</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="n">
+        <v>46258</v>
+      </c>
+      <c r="H114" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="I114" s="2" t="n"/>
+      <c r="J114" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>374</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service scheduled or reactive task 113</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0114</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Tampines Centre</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Ben Lim</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="n">
+        <v>46257</v>
+      </c>
+      <c r="H115" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="I115" s="2" t="n"/>
+      <c r="J115" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>409.5</v>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service scheduled or reactive task 114</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0115</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Chloe Goh</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="n">
+        <v>46256</v>
+      </c>
+      <c r="H116" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="I116" s="2" t="n"/>
+      <c r="J116" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>445</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service scheduled or reactive task 115</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0116</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Lee</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="n">
+        <v>46255</v>
+      </c>
+      <c r="H117" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="I117" s="4" t="n">
+        <v>46268</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>480.5</v>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>Pump Service scheduled or reactive task 116</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0117</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Paya Lebar Office</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Elena Ong</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="n">
+        <v>46254</v>
+      </c>
+      <c r="H118" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="I118" s="4" t="n">
+        <v>46268</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>516</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 117</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0118</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Farid Rahman</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="n">
+        <v>46253</v>
+      </c>
+      <c r="H119" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="I119" s="2" t="n"/>
+      <c r="J119" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 118</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0119</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Grace Ng</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="n">
+        <v>46252</v>
+      </c>
+      <c r="H120" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="I120" s="2" t="n"/>
+      <c r="J120" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 119</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0120</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Changi Workshop</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Hari Kumar</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="n">
+        <v>46251</v>
+      </c>
+      <c r="H121" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="I121" s="2" t="n"/>
+      <c r="J121" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 120</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0005</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Elena Ong</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="n">
+        <v>46286</v>
+      </c>
+      <c r="H122" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I122" s="2" t="n"/>
+      <c r="J122" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>Valve Repair scheduled or reactive task 005</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>WO-2026-0020</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Jurong Depot</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Lee</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="n">
+        <v>46271</v>
+      </c>
+      <c r="H123" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="I123" s="2" t="n"/>
+      <c r="J123" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>Meter Service scheduled or reactive task 020</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7090,7 +13744,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7295,7 +13949,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7473,7 +14127,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7536,7 +14190,7 @@
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>WORD COPILOT:
-From this selected verified Northstar Water Services operations brief, extract a handoff table with reporting date, filter scope, total, closed, cancelled, backlog, overdue, unassigned backlog and recorded cost. Separate facts, proposed next actions and open decisions. Keep every value traceable to the supplied brief.</t>
+Make a short table of the key numbers in this document: date, total, closed, cancelled, backlog, overdue, unassigned backlog and cost. Show it here in the chat and don’t change the document.</t>
         </is>
       </c>
     </row>
@@ -7554,7 +14208,7 @@
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>POWERPOINT COPILOT:
-Using this verified Northstar Word brief, create a four-slide initial update: scope and portfolio; backlog and overdue work; current assignments and proposed actions; decision required. Use the existing white/navy/blue design. Preserve all verified metrics. Add source/date notes. Do not invent completed work, savings or approved reassignment.</t>
+Fill these 4 slides from the uploaded Northstar_Operations_Brief.docx: 1 scope and totals, 2 backlog and overdue work, 3 unassigned jobs and proposed actions, 4 the decision needed. Keep the design and use only numbers from the brief.</t>
         </is>
       </c>
     </row>
@@ -7572,7 +14226,7 @@
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>POWERPOINT COPILOT:
-Audit these four Northstar Water Services slides against the selected verified operations brief. For each numeric claim give the source, date and scope; flag unsupported service-restoration, safety, customer-impact or approval claims. Propose corrections without changing the checked values.</t>
+Check these 4 slides against the uploaded brief. List any number that is wrong and give the correct number.</t>
         </is>
       </c>
     </row>
@@ -7590,8 +14244,8 @@
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>OUTLOOK COPILOT:
-Draft a concise reply to the synthetic thread quoted below, using the verified Northstar brief and these checked metrics. State the 30 September 2026 scope, backlog/overdue findings, proposed next actions and the decision requested. Explain that assignments are unapproved proposals. Do not claim the attachments have been sent. Keep as a draft.
-THREAD (synthetic, do not send):
+Write a short reply to the email below. Use these numbers for 30 September 2026: 120 total, 48 closed, 12 cancelled, 60 backlog, 50 overdue, 6 unassigned, cost S$35,827.50. Say what we found, what we propose next and what decision we need. Say that any new assignment is only a proposal, not approved.
+EMAIL (fictional):
 2026-09-29 09:00 Operations manager: Please prepare the 30 September portfolio snapshot; show open work by site, category and current assignment.
 2026-09-29 10:15 Supervisor: Check overdue jobs before proposing reassignment. Available hours are planning inputs, not approval.
 2026-09-30 08:30 Analyst: The source export is in the workbook. No new assignment has been approved. Please produce a Word brief and a short PowerPoint update, then prepare a draft reply.</t>
@@ -7601,67 +14255,23 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Step 6</t>
+          <t>Step 5</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>WORD COPILOT</t>
+          <t xml:space="preserve">Total </t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>WORD COPILOT:
-Compare these pasted PowerPoint and Outlook summaries with this verified Word brief. List inconsistent figures, status definitions, dates, owner claims or approved-action wording. Do not resolve a conflict by guessing. Return a discrepancy table with source and correction needed.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Formula / evidence</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Total clean rows</t>
-        </is>
-      </c>
-      <c r="B2" s="2">
-        <f>ROWS(tblWorkOrders[Work_Order_ID])</f>
-      </c>
-      <c r="C2" s="2"/>
+          <t>Total : 120
+Backlog : 60
+Overdue : 50
+Unassigned : 6
+Cost : S$35,827.50</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7674,7 +14284,160 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Formula / evidence</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Total clean rows</t>
+        </is>
+      </c>
+      <c r="B2" s="2">
+        <f>ROWS(tblWorkOrders[Work_Order_ID])</f>
+      </c>
+      <c r="C2" s="2">
+        <f>IF(B2=Control!B3,"PASS","FAIL")</f>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="B3" s="2">
+        <f>COUNTIFS(tblWorkOrders[Status],"Closed")</f>
+      </c>
+      <c r="C3" s="2">
+        <f>IF(B3=Control!B4,"PASS","FAIL")</f>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="B4" s="2">
+        <f>COUNTIFS(tblWorkOrders[Status],"Cancelled")</f>
+      </c>
+      <c r="C4" s="2">
+        <f>IF(B4=Control!B5,"PASS","FAIL")</f>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Backlog (neither Closed nor Cancelled)</t>
+        </is>
+      </c>
+      <c r="B5" s="2">
+        <f>COUNTIFS(tblWorkOrders[Status],"&lt;&gt;Closed",tblWorkOrders[Status],"&lt;&gt;Cancelled")</f>
+      </c>
+      <c r="C5" s="2">
+        <f>IF(B5=Control!B6,"PASS","FAIL")</f>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Overdue backlog (Due_Date before Report_Date)</t>
+        </is>
+      </c>
+      <c r="B6" s="2">
+        <f>COUNTIFS(tblWorkOrders[Status],"&lt;&gt;Closed",tblWorkOrders[Status],"&lt;&gt;Cancelled",tblWorkOrders[Due_Date],"&lt;"&amp;Control!$B$2)</f>
+      </c>
+      <c r="C6" s="2">
+        <f>IF(B6=Control!B7,"PASS","FAIL")</f>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned backlog (blank Assigned_To)</t>
+        </is>
+      </c>
+      <c r="B7" s="2">
+        <f>COUNTIFS(tblWorkOrders[Status],"&lt;&gt;Closed",tblWorkOrders[Status],"&lt;&gt;Cancelled",tblWorkOrders[Assigned_To],"")</f>
+      </c>
+      <c r="C7" s="2">
+        <f>IF(B7=Control!B8,"PASS","FAIL")</f>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Recorded cost SGD</t>
+        </is>
+      </c>
+      <c r="B8" s="6">
+        <f>SUM(tblWorkOrders[Cost_SGD])</f>
+      </c>
+      <c r="C8" s="2">
+        <f>IF(B8=Control!B11,"PASS","FAIL")</f>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Identity: total = closed + cancelled + backlog</t>
+        </is>
+      </c>
+      <c r="B9" s="2">
+        <f>B3+B4+B5</f>
+      </c>
+      <c r="C9" s="2">
+        <f>IF(B9=B2,"PASS","FAIL")</f>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Duplicate Work_Order_ID values</t>
+        </is>
+      </c>
+      <c r="B10" s="2">
+        <f>SUMPRODUCT(--(COUNTIF(tblWorkOrders[Work_Order_ID],tblWorkOrders[Work_Order_ID])&gt;1))</f>
+      </c>
+      <c r="C10" s="2">
+        <f>IF(B10=0,"PASS","FAIL")</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -7735,6 +14498,477 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Lab 1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Step 3</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Exact duplicate records removed</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2 (WO-2026-0005, WO-2026-0020)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2 (WO-2026-0005, WO-2026-0020)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Northstar_Work_Orders.xlsx, tblWorkOrders, all filters All</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Lab 1 model answer</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Lab 1</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Step 3</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Category labels standardised</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2 (WO-2026-0004, WO-2026-0013)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2 (WO-2026-0004, WO-2026-0013)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Northstar_Work_Orders.xlsx, tblWorkOrders, all filters All</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Lab 1 model answer</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Lab 1</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Step 4</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Total work orders</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Northstar_Work_Orders.xlsx, tblWorkOrders, all filters All</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Lab 1 model answer</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Lab 1</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Step 4</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Northstar_Work_Orders.xlsx, tblWorkOrders, all filters All</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Lab 1 model answer</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Lab 1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Step 4</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Northstar_Work_Orders.xlsx, tblWorkOrders, all filters All</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Lab 1 model answer</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Lab 1</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Step 4</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Northstar_Work_Orders.xlsx, tblWorkOrders, all filters All</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Lab 1 model answer</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Lab 1</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Step 4</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Overdue backlog</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Northstar_Work_Orders.xlsx, tblWorkOrders, all filters All</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Lab 1 model answer</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Lab 1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Step 4</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned backlog</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Northstar_Work_Orders.xlsx, tblWorkOrders, all filters All</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Lab 1 model answer</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Lab 1</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Step 4</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Recorded cost SGD</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>S$35,827.50</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>S$35,827.50</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Northstar_Work_Orders.xlsx, tblWorkOrders, all filters All</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Lab 1 model answer</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Lab 1</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Step 4</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Identity total = closed + cancelled + backlog</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>120 = 48 + 12 + 60</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>120 = 48 + 12 + 60</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Northstar_Work_Orders.xlsx, tblWorkOrders, all filters All</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Lab 1 model answer</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Lab 1</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Step 6</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Word brief figures agree with Checks</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>All 8 figures match</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>All 8 figures match</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Northstar_Work_Orders.xlsx, tblWorkOrders, all filters All</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Lab 1 model answer</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/labs/lab-02-word-to-powerpoint-and-outlook/data/Northstar_Work_Orders.xlsx
+++ b/labs/lab-02-word-to-powerpoint-and-outlook/data/Northstar_Work_Orders.xlsx
@@ -162,9 +162,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblWorkOrders" displayName="tblWorkOrders" ref="A1:M121" headerRowCount="1">
-  <autoFilter ref="A1:M121"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblWorkOrders" displayName="tblWorkOrders" ref="A1:N121" headerRowCount="1">
+  <autoFilter ref="A1:N121"/>
+  <tableColumns count="14">
     <tableColumn id="1" name="Work_Order_ID"/>
     <tableColumn id="2" name="Site"/>
     <tableColumn id="3" name="Job_Category"/>
@@ -178,6 +178,7 @@
     <tableColumn id="11" name="Actual_Hours"/>
     <tableColumn id="12" name="Cost_SGD"/>
     <tableColumn id="13" name="Description"/>
+    <tableColumn id="14" name="Failure_Mode"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -585,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M123"/>
+  <dimension ref="A1:N123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -601,6 +602,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -669,6 +671,11 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Failure_Mode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -724,6 +731,11 @@
           <t>Leak Repair scheduled or reactive task 001</t>
         </is>
       </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -777,6 +789,11 @@
       <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 002</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -832,6 +849,11 @@
           <t>Leak Repair scheduled or reactive task 003</t>
         </is>
       </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -885,6 +907,11 @@
           <t>Leak Repair scheduled or reactive task 004</t>
         </is>
       </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -938,6 +965,11 @@
           <t>Valve Repair scheduled or reactive task 005</t>
         </is>
       </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -993,6 +1025,11 @@
           <t>Valve Repair scheduled or reactive task 006</t>
         </is>
       </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1046,6 +1083,11 @@
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 007</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -1101,6 +1143,11 @@
           <t>Valve Repair scheduled or reactive task 008</t>
         </is>
       </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1154,6 +1201,11 @@
           <t>Pipe Replacement scheduled or reactive task 009</t>
         </is>
       </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1207,6 +1259,11 @@
           <t>Pipe Replacement scheduled or reactive task 010</t>
         </is>
       </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1262,6 +1319,11 @@
           <t>Pipe Replacement scheduled or reactive task 011</t>
         </is>
       </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1315,6 +1377,11 @@
       <c r="M13" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 012</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -1366,6 +1433,11 @@
           <t>Pump Service scheduled or reactive task 013</t>
         </is>
       </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1419,6 +1491,11 @@
           <t>Pump Service scheduled or reactive task 014</t>
         </is>
       </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1472,6 +1549,11 @@
           <t>Pump Service scheduled or reactive task 015</t>
         </is>
       </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1527,6 +1609,11 @@
           <t>Pump Service scheduled or reactive task 016</t>
         </is>
       </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1580,6 +1667,11 @@
       <c r="M18" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 017</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -1635,6 +1727,11 @@
           <t>Meter Service scheduled or reactive task 018</t>
         </is>
       </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1688,6 +1785,11 @@
           <t>Meter Service scheduled or reactive task 019</t>
         </is>
       </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1741,6 +1843,11 @@
           <t>Meter Service scheduled or reactive task 020</t>
         </is>
       </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Meter fault</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1796,6 +1903,11 @@
           <t>Leak Repair scheduled or reactive task 021</t>
         </is>
       </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1849,6 +1961,11 @@
       <c r="M23" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 022</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -1904,6 +2021,11 @@
           <t>Leak Repair scheduled or reactive task 023</t>
         </is>
       </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1957,6 +2079,11 @@
           <t>Leak Repair scheduled or reactive task 024</t>
         </is>
       </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2006,6 +2133,11 @@
           <t>Valve Repair scheduled or reactive task 025</t>
         </is>
       </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2061,6 +2193,11 @@
           <t>Valve Repair scheduled or reactive task 026</t>
         </is>
       </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2114,6 +2251,11 @@
       <c r="M28" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 027</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2311,11 @@
           <t>Valve Repair scheduled or reactive task 028</t>
         </is>
       </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2222,6 +2369,11 @@
           <t>Pipe Replacement scheduled or reactive task 029</t>
         </is>
       </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2275,6 +2427,11 @@
           <t>Pipe Replacement scheduled or reactive task 030</t>
         </is>
       </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2330,6 +2487,11 @@
           <t>Pipe Replacement scheduled or reactive task 031</t>
         </is>
       </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2383,6 +2545,11 @@
       <c r="M33" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 032</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -2438,6 +2605,11 @@
           <t>Pump Service scheduled or reactive task 033</t>
         </is>
       </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2491,6 +2663,11 @@
           <t>Pump Service scheduled or reactive task 034</t>
         </is>
       </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2544,6 +2721,11 @@
           <t>Pump Service scheduled or reactive task 035</t>
         </is>
       </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2599,6 +2781,11 @@
           <t>Pump Service scheduled or reactive task 036</t>
         </is>
       </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2652,6 +2839,11 @@
       <c r="M38" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 037</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -2707,6 +2899,11 @@
           <t>Meter Service scheduled or reactive task 038</t>
         </is>
       </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2760,6 +2957,11 @@
           <t>Meter Service scheduled or reactive task 039</t>
         </is>
       </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Meter fault</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2813,6 +3015,11 @@
           <t>Meter Service scheduled or reactive task 040</t>
         </is>
       </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2868,6 +3075,11 @@
           <t>Leak Repair scheduled or reactive task 041</t>
         </is>
       </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2921,6 +3133,11 @@
       <c r="M43" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 042</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -2976,6 +3193,11 @@
           <t>Leak Repair scheduled or reactive task 043</t>
         </is>
       </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Third-party damage</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3029,6 +3251,11 @@
           <t>Leak Repair scheduled or reactive task 044</t>
         </is>
       </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3082,6 +3309,11 @@
           <t>Valve Repair scheduled or reactive task 045</t>
         </is>
       </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3137,6 +3369,11 @@
           <t>Valve Repair scheduled or reactive task 046</t>
         </is>
       </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3190,6 +3427,11 @@
       <c r="M48" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 047</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
         </is>
       </c>
     </row>
@@ -3245,6 +3487,11 @@
           <t>Valve Repair scheduled or reactive task 048</t>
         </is>
       </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3294,6 +3541,11 @@
           <t>Pipe Replacement scheduled or reactive task 049</t>
         </is>
       </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3347,6 +3599,11 @@
           <t>Pipe Replacement scheduled or reactive task 050</t>
         </is>
       </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3402,6 +3659,11 @@
           <t>Pipe Replacement scheduled or reactive task 051</t>
         </is>
       </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3455,6 +3717,11 @@
       <c r="M53" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 052</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -3510,6 +3777,11 @@
           <t>Pump Service scheduled or reactive task 053</t>
         </is>
       </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3563,6 +3835,11 @@
           <t>Pump Service scheduled or reactive task 054</t>
         </is>
       </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3616,6 +3893,11 @@
           <t>Pump Service scheduled or reactive task 055</t>
         </is>
       </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3671,6 +3953,11 @@
           <t>Pump Service scheduled or reactive task 056</t>
         </is>
       </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3724,6 +4011,11 @@
       <c r="M58" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 057</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -3779,6 +4071,11 @@
           <t>Meter Service scheduled or reactive task 058</t>
         </is>
       </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3832,6 +4129,11 @@
           <t>Meter Service scheduled or reactive task 059</t>
         </is>
       </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>Blockage</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3885,6 +4187,11 @@
           <t>Meter Service scheduled or reactive task 060</t>
         </is>
       </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3940,6 +4247,11 @@
           <t>Leak Repair scheduled or reactive task 061</t>
         </is>
       </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3993,6 +4305,11 @@
       <c r="M63" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 062</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -4048,6 +4365,11 @@
           <t>Leak Repair scheduled or reactive task 063</t>
         </is>
       </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4101,6 +4423,11 @@
           <t>Leak Repair scheduled or reactive task 064</t>
         </is>
       </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4154,6 +4481,11 @@
           <t>Valve Repair scheduled or reactive task 065</t>
         </is>
       </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4209,6 +4541,11 @@
           <t>Valve Repair scheduled or reactive task 066</t>
         </is>
       </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4262,6 +4599,11 @@
       <c r="M68" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 067</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -4317,6 +4659,11 @@
           <t>Valve Repair scheduled or reactive task 068</t>
         </is>
       </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4370,6 +4717,11 @@
           <t>Pipe Replacement scheduled or reactive task 069</t>
         </is>
       </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4423,6 +4775,11 @@
           <t>Pipe Replacement scheduled or reactive task 070</t>
         </is>
       </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4478,6 +4835,11 @@
           <t>Pipe Replacement scheduled or reactive task 071</t>
         </is>
       </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4531,6 +4893,11 @@
       <c r="M73" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 072</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -4582,6 +4949,11 @@
           <t>Pump Service scheduled or reactive task 073</t>
         </is>
       </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4635,6 +5007,11 @@
           <t>Pump Service scheduled or reactive task 074</t>
         </is>
       </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4688,6 +5065,11 @@
           <t>Pump Service scheduled or reactive task 075</t>
         </is>
       </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4743,6 +5125,11 @@
           <t>Pump Service scheduled or reactive task 076</t>
         </is>
       </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4796,6 +5183,11 @@
       <c r="M78" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 077</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -4851,6 +5243,11 @@
           <t>Meter Service scheduled or reactive task 078</t>
         </is>
       </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Meter fault</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4904,6 +5301,11 @@
           <t>Meter Service scheduled or reactive task 079</t>
         </is>
       </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -4957,6 +5359,11 @@
           <t>Meter Service scheduled or reactive task 080</t>
         </is>
       </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -5012,6 +5419,11 @@
           <t>Leak Repair scheduled or reactive task 081</t>
         </is>
       </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5065,6 +5477,11 @@
       <c r="M83" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 082</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Third-party damage</t>
         </is>
       </c>
     </row>
@@ -5120,6 +5537,11 @@
           <t>Leak Repair scheduled or reactive task 083</t>
         </is>
       </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5173,6 +5595,11 @@
           <t>Leak Repair scheduled or reactive task 084</t>
         </is>
       </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5222,6 +5649,11 @@
           <t>Valve Repair scheduled or reactive task 085</t>
         </is>
       </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5277,6 +5709,11 @@
           <t>Valve Repair scheduled or reactive task 086</t>
         </is>
       </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -5330,6 +5767,11 @@
       <c r="M88" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 087</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -5385,6 +5827,11 @@
           <t>Valve Repair scheduled or reactive task 088</t>
         </is>
       </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5438,6 +5885,11 @@
           <t>Pipe Replacement scheduled or reactive task 089</t>
         </is>
       </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -5491,6 +5943,11 @@
           <t>Pipe Replacement scheduled or reactive task 090</t>
         </is>
       </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -5546,6 +6003,11 @@
           <t>Pipe Replacement scheduled or reactive task 091</t>
         </is>
       </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -5599,6 +6061,11 @@
       <c r="M93" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 092</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -5654,6 +6121,11 @@
           <t>Pump Service scheduled or reactive task 093</t>
         </is>
       </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -5707,6 +6179,11 @@
           <t>Pump Service scheduled or reactive task 094</t>
         </is>
       </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -5760,6 +6237,11 @@
           <t>Pump Service scheduled or reactive task 095</t>
         </is>
       </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -5815,6 +6297,11 @@
           <t>Pump Service scheduled or reactive task 096</t>
         </is>
       </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -5868,6 +6355,11 @@
       <c r="M98" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 097</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -5923,6 +6415,11 @@
           <t>Meter Service scheduled or reactive task 098</t>
         </is>
       </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Blockage</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -5976,6 +6473,11 @@
           <t>Meter Service scheduled or reactive task 099</t>
         </is>
       </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -6029,6 +6531,11 @@
           <t>Meter Service scheduled or reactive task 100</t>
         </is>
       </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -6084,6 +6591,11 @@
           <t>Leak Repair scheduled or reactive task 101</t>
         </is>
       </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -6137,6 +6649,11 @@
       <c r="M103" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 102</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -6192,6 +6709,11 @@
           <t>Leak Repair scheduled or reactive task 103</t>
         </is>
       </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -6245,6 +6767,11 @@
           <t>Leak Repair scheduled or reactive task 104</t>
         </is>
       </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -6298,6 +6825,11 @@
           <t>Valve Repair scheduled or reactive task 105</t>
         </is>
       </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -6353,6 +6885,11 @@
           <t>Valve Repair scheduled or reactive task 106</t>
         </is>
       </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -6406,6 +6943,11 @@
       <c r="M108" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 107</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -6461,6 +7003,11 @@
           <t>Valve Repair scheduled or reactive task 108</t>
         </is>
       </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -6510,6 +7057,11 @@
           <t>Pipe Replacement scheduled or reactive task 109</t>
         </is>
       </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -6563,6 +7115,11 @@
           <t>Pipe Replacement scheduled or reactive task 110</t>
         </is>
       </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -6618,6 +7175,11 @@
           <t>Pipe Replacement scheduled or reactive task 111</t>
         </is>
       </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -6671,6 +7233,11 @@
       <c r="M113" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 112</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -6726,6 +7293,11 @@
           <t>Pump Service scheduled or reactive task 113</t>
         </is>
       </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -6779,6 +7351,11 @@
           <t>Pump Service scheduled or reactive task 114</t>
         </is>
       </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -6832,6 +7409,11 @@
           <t>Pump Service scheduled or reactive task 115</t>
         </is>
       </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -6887,6 +7469,11 @@
           <t>Pump Service scheduled or reactive task 116</t>
         </is>
       </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -6940,6 +7527,11 @@
       <c r="M118" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 117</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Meter fault</t>
         </is>
       </c>
     </row>
@@ -6995,6 +7587,11 @@
           <t>Meter Service scheduled or reactive task 118</t>
         </is>
       </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -7048,6 +7645,11 @@
           <t>Meter Service scheduled or reactive task 119</t>
         </is>
       </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -7101,6 +7703,11 @@
           <t>Meter Service scheduled or reactive task 120</t>
         </is>
       </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -7154,6 +7761,11 @@
           <t>Valve Repair scheduled or reactive task 005</t>
         </is>
       </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -7205,6 +7817,11 @@
       <c r="M123" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 020</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>Meter fault</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M121"/>
+  <dimension ref="A1:N121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -7235,6 +7852,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7303,6 +7921,11 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Failure_Mode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -7358,6 +7981,11 @@
           <t>Leak Repair scheduled or reactive task 001</t>
         </is>
       </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -7411,6 +8039,11 @@
       <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 002</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -7466,6 +8099,11 @@
           <t>Leak Repair scheduled or reactive task 003</t>
         </is>
       </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -7519,6 +8157,11 @@
           <t>Leak Repair scheduled or reactive task 004</t>
         </is>
       </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -7572,6 +8215,11 @@
           <t>Valve Repair scheduled or reactive task 005</t>
         </is>
       </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -7627,6 +8275,11 @@
           <t>Valve Repair scheduled or reactive task 006</t>
         </is>
       </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -7680,6 +8333,11 @@
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 007</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -7735,6 +8393,11 @@
           <t>Valve Repair scheduled or reactive task 008</t>
         </is>
       </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -7788,6 +8451,11 @@
           <t>Pipe Replacement scheduled or reactive task 009</t>
         </is>
       </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -7841,6 +8509,11 @@
           <t>Pipe Replacement scheduled or reactive task 010</t>
         </is>
       </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -7896,6 +8569,11 @@
           <t>Pipe Replacement scheduled or reactive task 011</t>
         </is>
       </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -7949,6 +8627,11 @@
       <c r="M13" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 012</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -8000,6 +8683,11 @@
           <t>Pump Service scheduled or reactive task 013</t>
         </is>
       </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -8053,6 +8741,11 @@
           <t>Pump Service scheduled or reactive task 014</t>
         </is>
       </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -8106,6 +8799,11 @@
           <t>Pump Service scheduled or reactive task 015</t>
         </is>
       </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -8161,6 +8859,11 @@
           <t>Pump Service scheduled or reactive task 016</t>
         </is>
       </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -8214,6 +8917,11 @@
       <c r="M18" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 017</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -8269,6 +8977,11 @@
           <t>Meter Service scheduled or reactive task 018</t>
         </is>
       </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -8322,6 +9035,11 @@
           <t>Meter Service scheduled or reactive task 019</t>
         </is>
       </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -8375,6 +9093,11 @@
           <t>Meter Service scheduled or reactive task 020</t>
         </is>
       </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Meter fault</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -8430,6 +9153,11 @@
           <t>Leak Repair scheduled or reactive task 021</t>
         </is>
       </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -8483,6 +9211,11 @@
       <c r="M23" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 022</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -8538,6 +9271,11 @@
           <t>Leak Repair scheduled or reactive task 023</t>
         </is>
       </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -8591,6 +9329,11 @@
           <t>Leak Repair scheduled or reactive task 024</t>
         </is>
       </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -8640,6 +9383,11 @@
           <t>Valve Repair scheduled or reactive task 025</t>
         </is>
       </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -8695,6 +9443,11 @@
           <t>Valve Repair scheduled or reactive task 026</t>
         </is>
       </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -8748,6 +9501,11 @@
       <c r="M28" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 027</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -8803,6 +9561,11 @@
           <t>Valve Repair scheduled or reactive task 028</t>
         </is>
       </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -8856,6 +9619,11 @@
           <t>Pipe Replacement scheduled or reactive task 029</t>
         </is>
       </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -8909,6 +9677,11 @@
           <t>Pipe Replacement scheduled or reactive task 030</t>
         </is>
       </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -8964,6 +9737,11 @@
           <t>Pipe Replacement scheduled or reactive task 031</t>
         </is>
       </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -9017,6 +9795,11 @@
       <c r="M33" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 032</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -9072,6 +9855,11 @@
           <t>Pump Service scheduled or reactive task 033</t>
         </is>
       </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -9125,6 +9913,11 @@
           <t>Pump Service scheduled or reactive task 034</t>
         </is>
       </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -9178,6 +9971,11 @@
           <t>Pump Service scheduled or reactive task 035</t>
         </is>
       </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -9233,6 +10031,11 @@
           <t>Pump Service scheduled or reactive task 036</t>
         </is>
       </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -9286,6 +10089,11 @@
       <c r="M38" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 037</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -9341,6 +10149,11 @@
           <t>Meter Service scheduled or reactive task 038</t>
         </is>
       </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -9394,6 +10207,11 @@
           <t>Meter Service scheduled or reactive task 039</t>
         </is>
       </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Meter fault</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -9447,6 +10265,11 @@
           <t>Meter Service scheduled or reactive task 040</t>
         </is>
       </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -9502,6 +10325,11 @@
           <t>Leak Repair scheduled or reactive task 041</t>
         </is>
       </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -9555,6 +10383,11 @@
       <c r="M43" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 042</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -9610,6 +10443,11 @@
           <t>Leak Repair scheduled or reactive task 043</t>
         </is>
       </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Third-party damage</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -9663,6 +10501,11 @@
           <t>Leak Repair scheduled or reactive task 044</t>
         </is>
       </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9716,6 +10559,11 @@
           <t>Valve Repair scheduled or reactive task 045</t>
         </is>
       </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9771,6 +10619,11 @@
           <t>Valve Repair scheduled or reactive task 046</t>
         </is>
       </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9824,6 +10677,11 @@
       <c r="M48" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 047</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
         </is>
       </c>
     </row>
@@ -9879,6 +10737,11 @@
           <t>Valve Repair scheduled or reactive task 048</t>
         </is>
       </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9928,6 +10791,11 @@
           <t>Pipe Replacement scheduled or reactive task 049</t>
         </is>
       </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9981,6 +10849,11 @@
           <t>Pipe Replacement scheduled or reactive task 050</t>
         </is>
       </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10036,6 +10909,11 @@
           <t>Pipe Replacement scheduled or reactive task 051</t>
         </is>
       </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10089,6 +10967,11 @@
       <c r="M53" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 052</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -10144,6 +11027,11 @@
           <t>Pump Service scheduled or reactive task 053</t>
         </is>
       </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10197,6 +11085,11 @@
           <t>Pump Service scheduled or reactive task 054</t>
         </is>
       </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10250,6 +11143,11 @@
           <t>Pump Service scheduled or reactive task 055</t>
         </is>
       </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10305,6 +11203,11 @@
           <t>Pump Service scheduled or reactive task 056</t>
         </is>
       </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10358,6 +11261,11 @@
       <c r="M58" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 057</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -10413,6 +11321,11 @@
           <t>Meter Service scheduled or reactive task 058</t>
         </is>
       </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10466,6 +11379,11 @@
           <t>Meter Service scheduled or reactive task 059</t>
         </is>
       </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>Blockage</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -10519,6 +11437,11 @@
           <t>Meter Service scheduled or reactive task 060</t>
         </is>
       </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -10574,6 +11497,11 @@
           <t>Leak Repair scheduled or reactive task 061</t>
         </is>
       </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -10627,6 +11555,11 @@
       <c r="M63" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 062</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -10682,6 +11615,11 @@
           <t>Leak Repair scheduled or reactive task 063</t>
         </is>
       </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -10735,6 +11673,11 @@
           <t>Leak Repair scheduled or reactive task 064</t>
         </is>
       </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -10788,6 +11731,11 @@
           <t>Valve Repair scheduled or reactive task 065</t>
         </is>
       </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -10843,6 +11791,11 @@
           <t>Valve Repair scheduled or reactive task 066</t>
         </is>
       </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -10896,6 +11849,11 @@
       <c r="M68" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 067</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -10951,6 +11909,11 @@
           <t>Valve Repair scheduled or reactive task 068</t>
         </is>
       </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -11004,6 +11967,11 @@
           <t>Pipe Replacement scheduled or reactive task 069</t>
         </is>
       </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -11057,6 +12025,11 @@
           <t>Pipe Replacement scheduled or reactive task 070</t>
         </is>
       </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -11112,6 +12085,11 @@
           <t>Pipe Replacement scheduled or reactive task 071</t>
         </is>
       </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -11165,6 +12143,11 @@
       <c r="M73" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 072</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -11216,6 +12199,11 @@
           <t>Pump Service scheduled or reactive task 073</t>
         </is>
       </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -11269,6 +12257,11 @@
           <t>Pump Service scheduled or reactive task 074</t>
         </is>
       </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -11322,6 +12315,11 @@
           <t>Pump Service scheduled or reactive task 075</t>
         </is>
       </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -11377,6 +12375,11 @@
           <t>Pump Service scheduled or reactive task 076</t>
         </is>
       </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -11430,6 +12433,11 @@
       <c r="M78" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 077</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -11485,6 +12493,11 @@
           <t>Meter Service scheduled or reactive task 078</t>
         </is>
       </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Meter fault</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -11538,6 +12551,11 @@
           <t>Meter Service scheduled or reactive task 079</t>
         </is>
       </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -11591,6 +12609,11 @@
           <t>Meter Service scheduled or reactive task 080</t>
         </is>
       </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -11646,6 +12669,11 @@
           <t>Leak Repair scheduled or reactive task 081</t>
         </is>
       </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -11699,6 +12727,11 @@
       <c r="M83" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 082</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Third-party damage</t>
         </is>
       </c>
     </row>
@@ -11754,6 +12787,11 @@
           <t>Leak Repair scheduled or reactive task 083</t>
         </is>
       </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -11807,6 +12845,11 @@
           <t>Leak Repair scheduled or reactive task 084</t>
         </is>
       </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -11856,6 +12899,11 @@
           <t>Valve Repair scheduled or reactive task 085</t>
         </is>
       </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -11911,6 +12959,11 @@
           <t>Valve Repair scheduled or reactive task 086</t>
         </is>
       </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -11964,6 +13017,11 @@
       <c r="M88" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 087</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -12019,6 +13077,11 @@
           <t>Valve Repair scheduled or reactive task 088</t>
         </is>
       </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -12072,6 +13135,11 @@
           <t>Pipe Replacement scheduled or reactive task 089</t>
         </is>
       </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -12125,6 +13193,11 @@
           <t>Pipe Replacement scheduled or reactive task 090</t>
         </is>
       </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -12180,6 +13253,11 @@
           <t>Pipe Replacement scheduled or reactive task 091</t>
         </is>
       </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -12233,6 +13311,11 @@
       <c r="M93" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 092</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -12288,6 +13371,11 @@
           <t>Pump Service scheduled or reactive task 093</t>
         </is>
       </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -12341,6 +13429,11 @@
           <t>Pump Service scheduled or reactive task 094</t>
         </is>
       </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -12394,6 +13487,11 @@
           <t>Pump Service scheduled or reactive task 095</t>
         </is>
       </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -12449,6 +13547,11 @@
           <t>Pump Service scheduled or reactive task 096</t>
         </is>
       </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -12502,6 +13605,11 @@
       <c r="M98" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 097</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -12557,6 +13665,11 @@
           <t>Meter Service scheduled or reactive task 098</t>
         </is>
       </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Blockage</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -12610,6 +13723,11 @@
           <t>Meter Service scheduled or reactive task 099</t>
         </is>
       </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -12663,6 +13781,11 @@
           <t>Meter Service scheduled or reactive task 100</t>
         </is>
       </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -12718,6 +13841,11 @@
           <t>Leak Repair scheduled or reactive task 101</t>
         </is>
       </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -12771,6 +13899,11 @@
       <c r="M103" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 102</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -12826,6 +13959,11 @@
           <t>Leak Repair scheduled or reactive task 103</t>
         </is>
       </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -12879,6 +14017,11 @@
           <t>Leak Repair scheduled or reactive task 104</t>
         </is>
       </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -12932,6 +14075,11 @@
           <t>Valve Repair scheduled or reactive task 105</t>
         </is>
       </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -12987,6 +14135,11 @@
           <t>Valve Repair scheduled or reactive task 106</t>
         </is>
       </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -13040,6 +14193,11 @@
       <c r="M108" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 107</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -13095,6 +14253,11 @@
           <t>Valve Repair scheduled or reactive task 108</t>
         </is>
       </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -13144,6 +14307,11 @@
           <t>Pipe Replacement scheduled or reactive task 109</t>
         </is>
       </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -13197,6 +14365,11 @@
           <t>Pipe Replacement scheduled or reactive task 110</t>
         </is>
       </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -13252,6 +14425,11 @@
           <t>Pipe Replacement scheduled or reactive task 111</t>
         </is>
       </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -13305,6 +14483,11 @@
       <c r="M113" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 112</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -13360,6 +14543,11 @@
           <t>Pump Service scheduled or reactive task 113</t>
         </is>
       </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -13413,6 +14601,11 @@
           <t>Pump Service scheduled or reactive task 114</t>
         </is>
       </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -13466,6 +14659,11 @@
           <t>Pump Service scheduled or reactive task 115</t>
         </is>
       </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -13521,6 +14719,11 @@
           <t>Pump Service scheduled or reactive task 116</t>
         </is>
       </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -13574,6 +14777,11 @@
       <c r="M118" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 117</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Meter fault</t>
         </is>
       </c>
     </row>
@@ -13629,6 +14837,11 @@
           <t>Meter Service scheduled or reactive task 118</t>
         </is>
       </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -13682,6 +14895,11 @@
           <t>Meter Service scheduled or reactive task 119</t>
         </is>
       </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -13733,6 +14951,11 @@
       <c r="M121" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 120</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
